--- a/parking_allocation.xlsx
+++ b/parking_allocation.xlsx
@@ -413,21 +413,31 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Flat Number</t>
+          <t>Flat</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Resident Name</t>
+          <t>Resident</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
+        <is>
+          <t>Vehicle Number</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Vehicle Type</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
         <is>
           <t>Parking Slot</t>
         </is>
@@ -441,46 +451,76 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Aparna</t>
+          <t>aparna</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Slot-9</t>
+          <t>8865</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Car</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Slot-8</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>203</t>
+          <t>201839</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Prem</t>
+          <t>prem</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Slot-4</t>
+          <t>3529</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Car</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Slot-3</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>303</t>
+          <t>301</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Harisha</t>
+          <t>harsha</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Slot-10</t>
+          <t>4632</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Car</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Slot-1</t>
         </is>
       </c>
     </row>
@@ -492,29 +532,49 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Sai</t>
+          <t>sai</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Slot-6</t>
+          <t>4637</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Car</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Slot-4</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>503</t>
+          <t xml:space="preserve">501 </t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Srinivas</t>
+          <t>srinivas</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Slot-2</t>
+          <t>7866</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Car</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Slot-10</t>
         </is>
       </c>
     </row>
